--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Беларусь, обл. Минская, р-н Минский, Боровлянский, д. 58/10, 24</t>
+          <t>Беларусь, Минская область, Королёв Стан</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Беларусь, Минская область, Королёв Стан</t>
+          <t>Беларусь, обл. Минская, р-н Минский, Боровлянский, д. 58/10, 24</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инфо" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО КОРОБАМ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ПО ТОВАРУ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/supplies/111336801-1.xlsx
+++ b/supplies/111336801-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
